--- a/artfynd/A 50825-2021 artfynd.xlsx
+++ b/artfynd/A 50825-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50825-2021 artfynd.xlsx
+++ b/artfynd/A 50825-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114357436</v>
+        <v>114357435</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>426355</v>
+        <v>426353</v>
       </c>
       <c r="R2" t="n">
-        <v>6608930</v>
+        <v>6608912</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -790,19 +785,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114357435</v>
+        <v>114357436</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -839,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>426353</v>
+        <v>426355</v>
       </c>
       <c r="R3" t="n">
-        <v>6608912</v>
+        <v>6608930</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,6 +888,121 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Molkomskogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114357434</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björndalsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>426348</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6608987</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nyed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Karlstads kommun - NVI Molkomskogen</t>
         </is>

--- a/artfynd/A 50825-2021 artfynd.xlsx
+++ b/artfynd/A 50825-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Karlstads kommun - NVI Molkomskogen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114357435</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Karlstads kommun - NVI Molkomskogen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114357436</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,8 +1022,18 @@
           <t>Karlstads kommun - NVI Molkomskogen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114357434</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>